--- a/data/raOutput/RebateRefreshOutput/Consolidated_RAO_Report_26Jun.xlsx
+++ b/data/raOutput/RebateRefreshOutput/Consolidated_RAO_Report_26Jun.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TC10" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC1706" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,11 +436,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC10</t>
+          <t>TC1706</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Extra rows in RPT_RPT8107702707903CZ_raOutput.xlsx</t>
+          <t>Extra rows in RPT_RPT9518641008898FM_raOutput.xlsx</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,7 +487,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Extra rows in TC10_Exc_RAO_SOT_9Apr.xlsx</t>
+          <t>Extra rows in TC1706_Exc_RAO_SOT_9Apr.xlsx</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -521,15 +521,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>169413013, 169418113, 169450114, 169450514, 169451714, 169452414, 169452514, 169477212, 173085910, 173088210, 173088710, 3089321, 3089421, 310620530, 310621030, 310621090, 456120130, 456120330, 50458057830, 50458057930, 50458057990, 50458058030, 58406003204, 597015230, 597015290, 597015330, 61874011530, 78069620, 78077720</t>
+          <t>74012402, 74012403, 74024302, 74055402, 74061602, 74081702, 74153903, 74379902, 74433902</t>
         </is>
       </c>
     </row>
@@ -570,24 +570,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G5||169450114||WEGOVY||ALTERNATIVE||B||B||N||N||M||30</t>
+          <t>PP_OO_DBMIRESP||74012402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>NO</t>
@@ -602,19 +598,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>NO</t>
@@ -624,24 +616,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G5||169450114||WEGOVY||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74012402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>NO</t>
@@ -656,19 +644,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>NO</t>
@@ -678,24 +662,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G5||169450514||WEGOVY||REBATABLE||B||B||N||N||M||30</t>
+          <t>PP_OO_DBMIRESP||74012402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>NO</t>
@@ -705,24 +685,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G5||169450514||WEGOVY||REBATABLE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>NO</t>
@@ -732,24 +708,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G5||169450514||WEGOVY||REBATABLE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>NO</t>
@@ -759,24 +731,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G5||169450514||WEGOVY||REBATABLE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>NO</t>
@@ -786,24 +754,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G5||169451714||WEGOVY||ALTERNATIVE||B||B||N||N||M||30</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>NO</t>
@@ -813,24 +777,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G5||169451714||WEGOVY||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>NO</t>
@@ -840,24 +800,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G5||169451714||WEGOVY||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>NO</t>
@@ -867,24 +823,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G5||169451714||WEGOVY||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>NO</t>
@@ -894,24 +846,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G5||169452414||WEGOVY||ALTERNATIVE||B||B||N||N||M||30</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>NO</t>
@@ -921,24 +869,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G5||169452414||WEGOVY||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>NO</t>
@@ -948,24 +892,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G5||169452414||WEGOVY||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74012403||HUMIRA PEN-CD/UC/HS STARTER||REBATABLE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>NO</t>
@@ -975,24 +915,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G5||169452414||WEGOVY||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74024302||HUMIRA||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1002,24 +938,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>G5||169452514||WEGOVY||REBATABLE||B||B||N||N||M||30</t>
+          <t>PP_OO_DBMIRESP||74024302||HUMIRA||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1029,24 +961,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>G5||169452514||WEGOVY||REBATABLE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74024302||HUMIRA||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1056,24 +984,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>G5||169452514||WEGOVY||REBATABLE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74024302||HUMIRA||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1083,24 +1007,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>G5||169452514||WEGOVY||REBATABLE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74024302||HUMIRA||REBATABLE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1110,24 +1030,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>G5||50458057930||XARELTO||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1137,24 +1053,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>G5||456120330||LINZESS||REBATABLE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1164,24 +1076,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>G5||173085910||BREO ELLIPTA||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1191,24 +1099,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>G5||173088210||BREO ELLIPTA||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1218,24 +1122,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>G5||173088210||BREO ELLIPTA||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1245,24 +1145,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>G5||169413013||OZEMPIC||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1272,24 +1168,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>G5||3089321||ELIQUIS||REBATABLE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1299,24 +1191,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>G5||310621030||FARXIGA||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1326,24 +1214,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>G5||597015230||JARDIANCE||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1353,24 +1237,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>G5||3089421||ELIQUIS||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1380,24 +1260,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>G5||78069620||ENTRESTO||AGGREGATE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1407,24 +1283,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>G5||50458058030||XARELTO||REBATABLE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1434,24 +1306,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>G5||310621030||FARXIGA||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1461,24 +1329,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>G5||310621090||FARXIGA||AGGREGATE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1488,24 +1352,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>G5||169418113||OZEMPIC||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74055402||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1515,24 +1375,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>G5||173085910||BREO ELLIPTA||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74061602||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1542,24 +1398,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>G5||169413013||OZEMPIC||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74061602||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1569,24 +1421,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>G5||597015330||JARDIANCE||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74061602||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1596,24 +1444,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>G5||173088710||TRELEGY ELLIPTA||REBATABLE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74061602||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1623,24 +1467,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>G5||169418113||OZEMPIC||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74061602||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1650,24 +1490,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>G5||173088710||TRELEGY ELLIPTA||REBATABLE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74081702||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1677,24 +1513,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>G5||3089421||ELIQUIS||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74081702||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1704,24 +1536,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>G5||61874011530||VRAYLAR||REBATABLE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74081702||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1731,24 +1559,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>G5||58406003204||ENBREL SURECLICK||REBATABLE||B||B||Y||Y||R||90</t>
+          <t>PP_OO_DBMIRESP||74081702||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1758,24 +1582,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>G5||50458057930||XARELTO||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74081702||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1785,24 +1605,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>G5||50458058030||XARELTO||REBATABLE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74153903||HUMIRA PEN-PS/UV STARTER||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1812,24 +1628,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>G5||597015230||JARDIANCE||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74153903||HUMIRA PEN-PS/UV STARTER||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1839,24 +1651,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>G5||50458058030||XARELTO||REBATABLE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74153903||HUMIRA PEN-PS/UV STARTER||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1866,24 +1674,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>G5||173088210||BREO ELLIPTA||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74153903||HUMIRA PEN-PS/UV STARTER||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1893,24 +1697,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>G5||169477212||OZEMPIC||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74153903||HUMIRA PEN-PS/UV STARTER||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1920,24 +1720,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>G5||310620530||FARXIGA||AGGREGATE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1947,24 +1743,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>G5||169477212||OZEMPIC||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1974,24 +1766,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>G5||3089321||ELIQUIS||REBATABLE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2001,24 +1789,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>G5||456120130||LINZESS||REBATABLE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2028,24 +1812,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>G5||597015330||JARDIANCE||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2055,24 +1835,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>G5||50458057930||XARELTO||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2082,24 +1858,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>G5||50458057830||XARELTO||REBATABLE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2109,24 +1881,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>G5||50458057990||XARELTO||REBATABLE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2136,24 +1904,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>G5||456120330||LINZESS||REBATABLE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2163,24 +1927,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>G5||173085910||BREO ELLIPTA||ALTERNATIVE||B||B||N||N||R||30</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2190,24 +1950,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>G5||169418113||OZEMPIC||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2217,24 +1973,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>G5||169413013||OZEMPIC||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2244,24 +1996,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>G5||169477212||OZEMPIC||ALTERNATIVE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2271,24 +2019,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>G5||78077720||ENTRESTO||AGGREGATE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2298,24 +2042,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>G5||3089321||ELIQUIS||REBATABLE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74379902||HUMIRA||ALTERNATIVE||B||B||Y||Y||R||90</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2325,24 +2065,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>G5||3089421||ELIQUIS||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2352,24 +2088,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>G5||310621030||FARXIGA||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2379,24 +2111,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>G5||310620530||FARXIGA||AGGREGATE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2406,24 +2134,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>G5||597015290||JARDIANCE||REBATABLE||B||B||N||N||M||90</t>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2433,24 +2157,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>G5||597015230||JARDIANCE||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||M||90</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>NO</t>
@@ -2460,25 +2180,228 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>G5||597015330||JARDIANCE||ALTERNATIVE||B||B||N||N||R||90</t>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shifted_QTY_Selected Excl Desc</t>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MFP 2026,2027</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>MFP 2026 &amp; 2027</t>
-        </is>
-      </c>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||30</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PP_OO_DBMIRESP||74433902||HUMIRA PEN||ALTERNATIVE||B||B||Y||Y||R||90</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Post-Shift + Hep C adj_Base  w/o Biosim Adj</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>$0.0</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
